--- a/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0003T0006Z000C1N17_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0003T0006Z000C1N17_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>43.24404194579947</v>
+        <v>7.027156816192414</v>
       </c>
       <c r="D2" t="n">
-        <v>44.34632347469176</v>
+        <v>7.206277564637412</v>
       </c>
       <c r="E2" t="n">
-        <v>9.045697293229878</v>
+        <v>1.469925810149855</v>
       </c>
       <c r="F2" t="n">
-        <v>9.185254170796373</v>
+        <v>1.492603802754411</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>22.84473404294066</v>
+        <v>3.712269281977857</v>
       </c>
       <c r="D3" t="n">
-        <v>22.74358674526513</v>
+        <v>3.695832846105584</v>
       </c>
       <c r="E3" t="n">
-        <v>9.045697293229878</v>
+        <v>1.469925810149855</v>
       </c>
       <c r="F3" t="n">
-        <v>9.185254170796373</v>
+        <v>1.492603802754411</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>5.929346381446134</v>
+        <v>0.9635187869849968</v>
       </c>
       <c r="D4" t="n">
-        <v>5.719450381206309</v>
+        <v>0.9294106869460252</v>
       </c>
       <c r="E4" t="n">
-        <v>9.045697293229878</v>
+        <v>1.469925810149855</v>
       </c>
       <c r="F4" t="n">
-        <v>9.185254170796373</v>
+        <v>1.492603802754411</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>34.16872427890956</v>
+        <v>5.552417695322805</v>
       </c>
       <c r="D5" t="n">
-        <v>33.42865850435187</v>
+        <v>5.43215700695718</v>
       </c>
       <c r="E5" t="n">
-        <v>9.045697293229878</v>
+        <v>1.469925810149855</v>
       </c>
       <c r="F5" t="n">
-        <v>9.185254170796373</v>
+        <v>1.492603802754411</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>34.97487382846047</v>
+        <v>5.683416997124827</v>
       </c>
       <c r="D6" t="n">
-        <v>34.2045379240131</v>
+        <v>5.558237412652129</v>
       </c>
       <c r="E6" t="n">
-        <v>9.045697293229878</v>
+        <v>1.469925810149855</v>
       </c>
       <c r="F6" t="n">
-        <v>9.185254170796373</v>
+        <v>1.492603802754411</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>37.02566826495795</v>
+        <v>6.016671093055667</v>
       </c>
       <c r="D7" t="n">
-        <v>36.63759664722695</v>
+        <v>5.953609455174379</v>
       </c>
       <c r="E7" t="n">
-        <v>9.045697293229878</v>
+        <v>1.469925810149855</v>
       </c>
       <c r="F7" t="n">
-        <v>9.185254170796373</v>
+        <v>1.492603802754411</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>36.8035324052389</v>
+        <v>5.980574015851321</v>
       </c>
       <c r="D8" t="n">
-        <v>36.1755051614527</v>
+        <v>5.878519588736065</v>
       </c>
       <c r="E8" t="n">
-        <v>9.045697293229878</v>
+        <v>1.469925810149855</v>
       </c>
       <c r="F8" t="n">
-        <v>9.185254170796373</v>
+        <v>1.492603802754411</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>31.42456284060671</v>
+        <v>5.106491461598591</v>
       </c>
       <c r="D9" t="n">
-        <v>31.06780500244361</v>
+        <v>5.048518312897087</v>
       </c>
       <c r="E9" t="n">
-        <v>9.045697293229878</v>
+        <v>1.469925810149855</v>
       </c>
       <c r="F9" t="n">
-        <v>9.185254170796373</v>
+        <v>1.492603802754411</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>35.76947692485372</v>
+        <v>5.812540000288729</v>
       </c>
       <c r="D10" t="n">
-        <v>35.86099237134405</v>
+        <v>5.827411260343409</v>
       </c>
       <c r="E10" t="n">
-        <v>9.045697293229878</v>
+        <v>1.469925810149855</v>
       </c>
       <c r="F10" t="n">
-        <v>9.185254170796373</v>
+        <v>1.492603802754411</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>34.0933303471841</v>
+        <v>5.540166181417416</v>
       </c>
       <c r="D11" t="n">
-        <v>34.23145698886773</v>
+        <v>5.562611760691006</v>
       </c>
       <c r="E11" t="n">
-        <v>9.045697293229878</v>
+        <v>1.469925810149855</v>
       </c>
       <c r="F11" t="n">
-        <v>9.185254170796373</v>
+        <v>1.492603802754411</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>31.58050615987526</v>
+        <v>5.131832250979731</v>
       </c>
       <c r="D12" t="n">
-        <v>32.39000180286718</v>
+        <v>5.263375292965917</v>
       </c>
       <c r="E12" t="n">
-        <v>9.045697293229878</v>
+        <v>1.469925810149855</v>
       </c>
       <c r="F12" t="n">
-        <v>9.185254170796373</v>
+        <v>1.492603802754411</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>35.32302705174549</v>
+        <v>5.739991895908642</v>
       </c>
       <c r="D13" t="n">
-        <v>36.12205922718341</v>
+        <v>5.869834624417304</v>
       </c>
       <c r="E13" t="n">
-        <v>9.045697293229878</v>
+        <v>1.469925810149855</v>
       </c>
       <c r="F13" t="n">
-        <v>9.185254170796373</v>
+        <v>1.492603802754411</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
